--- a/서버정보/20260727_리소스배포_테스트.xlsx
+++ b/서버정보/20260727_리소스배포_테스트.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF8D779-D737-45A3-9E22-F6C78FA079B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -28008,6 +28008,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -28151,22 +28166,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28182,28 +28206,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>